--- a/data/reports/2024-06-24/2024-06-24_duplicates.xlsx
+++ b/data/reports/2024-06-24/2024-06-24_duplicates.xlsx
@@ -145,7 +145,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004723</t>
+    <t>RMD0005813</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -161,28 +161,28 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>Glenn Dalgliesh</t>
+  </si>
+  <si>
+    <t>VP of Operations</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>'+14439121000</t>
+  </si>
+  <si>
+    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004723</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005813</t>
-  </si>
-  <si>
-    <t>Glenn Dalgliesh</t>
-  </si>
-  <si>
-    <t>VP of Operations</t>
-  </si>
-  <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>'+14439121000</t>
-  </si>
-  <si>
-    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004139</t>
@@ -225,10 +225,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>null
+null CA
+California</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -236,32 +258,10 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>U.S. Virgin Islands</t>
-  </si>
-  <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
-    <t>null
-null CA
-California</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
+    <t>RMD0009084</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,6 +318,12 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009205</t>
+  </si>
+  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -340,13 +346,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009084</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008869</t>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -469,10 +469,20 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>Edge Fibernet</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0005786</t>
-  </si>
-  <si>
-    <t>Edge Fibernet</t>
   </si>
   <si>
     <t>254 36th Street
@@ -483,16 +493,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005785</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0007488</t>
   </si>
   <si>
@@ -596,7 +596,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004701</t>
+    <t>RMD0003052</t>
   </si>
   <si>
     <t>Jaintel LLC</t>
@@ -606,15 +606,33 @@
 DE 19806-3334 Wilmington, United States</t>
   </si>
   <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Elayaraja Jinadoss</t>
   </si>
   <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>'+447341664829</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004701</t>
+  </si>
+  <si>
     <t>Operations Director</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
     <t>'+1 737 237 0913</t>
   </si>
   <si>
@@ -622,24 +640,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b1f3904a1b4138107ccf20ecac4bcbbf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003052</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+447341664829</t>
-  </si>
-  <si>
-    <t>2024-05-01</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0003053</t>
@@ -670,7 +670,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -681,32 +681,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -726,6 +700,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007384</t>
   </si>
   <si>
@@ -754,7 +754,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -764,6 +764,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -780,12 +786,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005569</t>
@@ -836,7 +836,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
+    <t>RMD0005297</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -849,6 +849,12 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
+  </si>
+  <si>
     <t>Syed Omar Farooq Shah</t>
   </si>
   <si>
@@ -858,13 +864,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
+    <t>RMD0005574</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -878,6 +878,22 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
+  </si>
+  <si>
+    <t>187 Plymouth Ave
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005585</t>
+  </si>
+  <si>
     <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
   </si>
   <si>
@@ -891,23 +907,7 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
-  </si>
-  <si>
-    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
-  </si>
-  <si>
-    <t>187 Plymouth Ave
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -993,7 +993,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
+    <t>RMD0007716</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1003,16 +1003,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007696</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007716</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1022,6 +1022,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1035,12 +1041,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1074,7 +1074,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1084,12 +1084,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1097,6 +1091,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008611</t>
   </si>
   <si>
@@ -1116,25 +1116,25 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008610</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008759</t>
@@ -6202,16 +6202,28 @@
         <v>46</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="M5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R5" s="1" t="s">
         <v>26</v>
       </c>
@@ -6219,16 +6231,16 @@
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1">
         <v>17118795</v>
@@ -6252,28 +6264,16 @@
         <v>46</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
         <v>26</v>
       </c>
@@ -6281,7 +6281,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6550,9 +6550,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>30</v>
@@ -6563,14 +6565,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6597,7 +6601,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6606,13 +6610,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>30</v>
@@ -6623,9 +6625,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6644,55 +6644,41 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6704,32 +6690,46 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R14" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6755,54 +6755,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6819,33 +6805,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -7011,13 +7011,13 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>127</v>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>26</v>
@@ -7348,7 +7348,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7496,55 +7496,61 @@
         <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J29" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="1">
         <v>30758643</v>
@@ -7556,34 +7562,28 @@
         <v>184</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>194</v>
@@ -7593,10 +7593,10 @@
         <v>39</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>26</v>
@@ -7625,7 +7625,7 @@
         <v>30</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -7671,7 +7671,7 @@
         <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -7689,14 +7689,14 @@
         <v>199</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>204</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>30</v>
@@ -7738,45 +7738,33 @@
       <c r="I33" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>215</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1">
         <v>31064850</v>
@@ -7794,30 +7782,42 @@
         <v>209</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R34" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1" t="s">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>30</v>
@@ -7949,48 +7949,34 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>237</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B38" s="1">
         <v>31124688</v>
@@ -8009,25 +7995,39 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="M38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>26</v>
@@ -8178,45 +8178,33 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q41" s="1"/>
       <c r="R41" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1">
         <v>31294614</v>
@@ -8236,24 +8224,36 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="M42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
+      <c r="Q42" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R42" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8285,48 +8285,42 @@
       <c r="H43" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="I43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="N43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B44" s="1">
         <v>31356652</v>
@@ -8347,14 +8341,18 @@
         <v>268</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>277</v>
       </c>
@@ -8362,22 +8360,24 @@
         <v>27</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U44" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V44" s="1" t="s">
         <v>278</v>
       </c>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>30</v>
@@ -8703,9 +8703,15 @@
       <c r="F51" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -8749,15 +8755,9 @@
       <c r="F52" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -8796,55 +8796,41 @@
         <v>313</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B54" s="1">
         <v>31445216</v>
@@ -8856,32 +8842,46 @@
         <v>313</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -9016,7 +9016,7 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -9033,12 +9033,12 @@
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B58" s="1">
         <v>31457815</v>
@@ -9062,7 +9062,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -9147,38 +9147,50 @@
         <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="M60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+        <v>339</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
+      <c r="Q60" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R60" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B61" s="1">
         <v>31475270</v>
@@ -9193,41 +9205,29 @@
         <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>348</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9274,7 +9274,7 @@
         <v>354</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>30</v>
@@ -9380,7 +9380,7 @@
         <v>366</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>30</v>
@@ -9738,7 +9738,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>30</v>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>30</v>
@@ -9944,7 +9944,7 @@
         <v>415</v>
       </c>
       <c r="Q75" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R75" s="1" t="s">
         <v>26</v>
@@ -9982,7 +9982,7 @@
         <v>419</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>420</v>
@@ -10004,7 +10004,7 @@
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>30</v>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="P77" s="1"/>
       <c r="Q77" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R77" s="1" t="s">
         <v>30</v>
@@ -10126,7 +10126,7 @@
         <v>438</v>
       </c>
       <c r="Q78" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>26</v>
@@ -10251,7 +10251,7 @@
         <v>30</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
@@ -10311,7 +10311,7 @@
         <v>245</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M82" s="1" t="s">
         <v>451</v>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="P82" s="1"/>
       <c r="Q82" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R82" s="1" t="s">
         <v>30</v>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="P83" s="1"/>
       <c r="Q83" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R83" s="1" t="s">
         <v>30</v>
@@ -10729,7 +10729,7 @@
         <v>30</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>28</v>
@@ -10871,7 +10871,7 @@
         <v>30</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
@@ -10880,21 +10880,21 @@
         <v>505</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L93" s="1" t="s">
         <v>506</v>
       </c>
       <c r="M93" s="1"/>
       <c r="N93" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O93" s="1" t="s">
         <v>507</v>
       </c>
       <c r="P93" s="1"/>
       <c r="Q93" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R93" s="1" t="s">
         <v>30</v>
@@ -10937,7 +10937,7 @@
         <v>59</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M94" s="1" t="s">
         <v>510</v>
@@ -11039,7 +11039,7 @@
         <v>30</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G96" s="1"/>
       <c r="H96" s="1"/>
@@ -11057,14 +11057,14 @@
         <v>523</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>524</v>
       </c>
       <c r="P96" s="1"/>
       <c r="Q96" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R96" s="1" t="s">
         <v>30</v>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="P100" s="1"/>
       <c r="Q100" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R100" s="1" t="s">
         <v>30</v>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="P101" s="1"/>
       <c r="Q101" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>30</v>
@@ -11350,13 +11350,13 @@
         <v>27</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H102" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>553</v>
@@ -11365,7 +11365,7 @@
         <v>59</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M102" s="1" t="s">
         <v>552</v>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>30</v>
@@ -11440,7 +11440,7 @@
       </c>
       <c r="P103" s="1"/>
       <c r="Q103" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>26</v>
@@ -11776,10 +11776,10 @@
         <v>603</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>602</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="P109" s="1"/>
       <c r="Q109" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R109" s="1" t="s">
         <v>30</v>
@@ -12046,13 +12046,13 @@
         <v>27</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J114" s="1" t="s">
         <v>633</v>
@@ -12136,7 +12136,7 @@
       </c>
       <c r="P115" s="1"/>
       <c r="Q115" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R115" s="1" t="s">
         <v>30</v>
@@ -12229,7 +12229,7 @@
         <v>653</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>649</v>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="P120" s="1"/>
       <c r="Q120" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R120" s="1" t="s">
         <v>30</v>
@@ -12590,7 +12590,7 @@
       </c>
       <c r="P123" s="1"/>
       <c r="Q123" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R123" s="1" t="s">
         <v>26</v>
@@ -12695,7 +12695,7 @@
         <v>706</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>703</v>
@@ -12807,7 +12807,7 @@
         <v>718</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>715</v>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="P128" s="1"/>
       <c r="Q128" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R128" s="1" t="s">
         <v>30</v>
@@ -12959,7 +12959,7 @@
         <v>30</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
@@ -13128,7 +13128,7 @@
       </c>
       <c r="P133" s="1"/>
       <c r="Q133" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R133" s="1" t="s">
         <v>30</v>
@@ -13223,7 +13223,7 @@
         <v>30</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G135" s="1" t="s">
         <v>28</v>
@@ -13247,7 +13247,7 @@
         <v>757</v>
       </c>
       <c r="N135" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O135" s="1" t="s">
         <v>760</v>
@@ -13312,7 +13312,7 @@
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R136" s="1" t="s">
         <v>30</v>
@@ -13355,7 +13355,7 @@
         <v>771</v>
       </c>
       <c r="L137" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>769</v>
@@ -13413,7 +13413,7 @@
         <v>245</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>775</v>
@@ -13546,7 +13546,7 @@
       </c>
       <c r="P140" s="1"/>
       <c r="Q140" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R140" s="1" t="s">
         <v>30</v>
@@ -13664,7 +13664,7 @@
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R142" s="1" t="s">
         <v>30</v>
@@ -13816,13 +13816,13 @@
         <v>27</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H145" s="1" t="s">
         <v>824</v>
       </c>
       <c r="I145" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J145" s="1" t="s">
         <v>825</v>
@@ -13831,7 +13831,7 @@
         <v>826</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M145" s="1" t="s">
         <v>823</v>
@@ -13895,7 +13895,7 @@
         <v>835</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M146" s="1" t="s">
         <v>836</v>
@@ -13939,7 +13939,7 @@
         <v>30</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>841</v>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="P148" s="1"/>
       <c r="Q148" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R148" s="1" t="s">
         <v>30</v>
@@ -14414,7 +14414,7 @@
       </c>
       <c r="P156" s="1"/>
       <c r="Q156" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R156" s="1" t="s">
         <v>30</v>
@@ -14474,7 +14474,7 @@
         <v>895</v>
       </c>
       <c r="Q157" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R157" s="1" t="s">
         <v>26</v>
@@ -14519,7 +14519,7 @@
         <v>901</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M158" s="1"/>
       <c r="N158" s="1" t="s">
@@ -14572,7 +14572,7 @@
         <v>907</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L159" s="1" t="s">
         <v>908</v>
@@ -14662,7 +14662,7 @@
         <v>27</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H161" s="1"/>
       <c r="I161" s="1"/>
@@ -14730,7 +14730,7 @@
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>26</v>
@@ -14761,7 +14761,7 @@
         <v>30</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>28</v>
@@ -14785,14 +14785,14 @@
         <v>928</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O163" s="1" t="s">
         <v>929</v>
       </c>
       <c r="P163" s="1"/>
       <c r="Q163" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R163" s="1" t="s">
         <v>30</v>
@@ -14826,7 +14826,7 @@
         <v>27</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H164" s="1" t="s">
         <v>933</v>
@@ -14854,7 +14854,7 @@
       </c>
       <c r="P164" s="1"/>
       <c r="Q164" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R164" s="1" t="s">
         <v>30</v>
@@ -14885,7 +14885,7 @@
         <v>30</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G165" s="1"/>
       <c r="H165" s="1"/>
@@ -14897,11 +14897,11 @@
         <v>59</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M165" s="1"/>
       <c r="N165" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O165" s="1" t="s">
         <v>941</v>
@@ -15089,7 +15089,7 @@
         <v>30</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G169" s="1"/>
       <c r="H169" s="1"/>
@@ -15098,21 +15098,21 @@
         <v>958</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L169" s="1" t="s">
         <v>203</v>
       </c>
       <c r="M169" s="1"/>
       <c r="N169" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O169" s="1" t="s">
         <v>959</v>
       </c>
       <c r="P169" s="1"/>
       <c r="Q169" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R169" s="1" t="s">
         <v>30</v>
@@ -15197,7 +15197,7 @@
         <v>59</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M171" s="1"/>
       <c r="N171" s="1" t="s">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="P171" s="1"/>
       <c r="Q171" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R171" s="1" t="s">
         <v>30</v>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="P172" s="1"/>
       <c r="Q172" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R172" s="1" t="s">
         <v>30</v>
@@ -15332,7 +15332,7 @@
       </c>
       <c r="P173" s="1"/>
       <c r="Q173" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R173" s="1" t="s">
         <v>30</v>
@@ -15384,7 +15384,7 @@
       </c>
       <c r="P174" s="1"/>
       <c r="Q174" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R174" s="1" t="s">
         <v>26</v>
@@ -15554,7 +15554,7 @@
       </c>
       <c r="P177" s="1"/>
       <c r="Q177" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R177" s="1" t="s">
         <v>30</v>
@@ -15616,7 +15616,7 @@
       </c>
       <c r="P178" s="1"/>
       <c r="Q178" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R178" s="1" t="s">
         <v>30</v>
@@ -15721,7 +15721,7 @@
         <v>1029</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M180" s="1" t="s">
         <v>1030</v>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="P180" s="1"/>
       <c r="Q180" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R180" s="1" t="s">
         <v>30</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="P182" s="1"/>
       <c r="Q182" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>30</v>
@@ -15886,13 +15886,13 @@
         <v>27</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H183" s="1" t="s">
         <v>1050</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J183" s="1"/>
       <c r="K183" s="1"/>
@@ -15958,7 +15958,7 @@
       </c>
       <c r="P184" s="1"/>
       <c r="Q184" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R184" s="1" t="s">
         <v>26</v>
@@ -16016,7 +16016,7 @@
       </c>
       <c r="P185" s="1"/>
       <c r="Q185" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R185" s="1" t="s">
         <v>26</v>
@@ -16112,13 +16112,13 @@
         <v>27</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H187" s="1" t="s">
         <v>1077</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J187" s="1"/>
       <c r="K187" s="1"/>
@@ -16279,7 +16279,7 @@
         <v>30</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
@@ -16297,14 +16297,14 @@
         <v>1095</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O190" s="1" t="s">
         <v>1096</v>
       </c>
       <c r="P190" s="1"/>
       <c r="Q190" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R190" s="1" t="s">
         <v>30</v>
@@ -16364,7 +16364,7 @@
       </c>
       <c r="P191" s="1"/>
       <c r="Q191" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R191" s="1" t="s">
         <v>30</v>
@@ -16405,7 +16405,7 @@
         <v>293</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M192" s="1" t="s">
         <v>1106</v>
@@ -16696,7 +16696,7 @@
         <v>1137</v>
       </c>
       <c r="K197" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L197" s="1" t="s">
         <v>1138</v>
@@ -16759,7 +16759,7 @@
         <v>165</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M198" s="1" t="s">
         <v>1147</v>
@@ -16772,7 +16772,7 @@
       </c>
       <c r="P198" s="1"/>
       <c r="Q198" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R198" s="1" t="s">
         <v>30</v>
@@ -16815,7 +16815,7 @@
         <v>59</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M199" s="1" t="s">
         <v>1154</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="P199" s="1"/>
       <c r="Q199" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R199" s="1" t="s">
         <v>30</v>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="P201" s="1"/>
       <c r="Q201" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R201" s="1" t="s">
         <v>30</v>
@@ -17031,7 +17031,7 @@
         <v>30</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G203" s="1"/>
       <c r="H203" s="1"/>
@@ -17043,18 +17043,18 @@
         <v>490</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M203" s="1"/>
       <c r="N203" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O203" s="1" t="s">
         <v>1178</v>
       </c>
       <c r="P203" s="1"/>
       <c r="Q203" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R203" s="1" t="s">
         <v>30</v>
@@ -17112,7 +17112,7 @@
       </c>
       <c r="P204" s="1"/>
       <c r="Q204" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R204" s="1" t="s">
         <v>30</v>
@@ -17157,7 +17157,7 @@
         <v>1191</v>
       </c>
       <c r="L205" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M205" s="1"/>
       <c r="N205" s="1" t="s">
@@ -17386,7 +17386,7 @@
       </c>
       <c r="P209" s="1"/>
       <c r="Q209" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R209" s="1" t="s">
         <v>30</v>
@@ -17444,7 +17444,7 @@
       </c>
       <c r="P210" s="1"/>
       <c r="Q210" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R210" s="1" t="s">
         <v>30</v>
@@ -17506,7 +17506,7 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>30</v>
@@ -17541,16 +17541,16 @@
         <v>30</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I212" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J212" s="1" t="s">
         <v>1235</v>
@@ -17565,7 +17565,7 @@
         <v>1234</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O212" s="1" t="s">
         <v>1237</v>
@@ -17607,7 +17607,7 @@
         <v>30</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G213" s="1" t="s">
         <v>1240</v>
@@ -17627,7 +17627,7 @@
         <v>1234</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>1237</v>
@@ -17742,10 +17742,10 @@
         <v>1254</v>
       </c>
       <c r="K215" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M215" s="1" t="s">
         <v>1255</v>
@@ -17820,7 +17820,7 @@
       </c>
       <c r="P216" s="1"/>
       <c r="Q216" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R216" s="1" t="s">
         <v>30</v>
@@ -17880,7 +17880,7 @@
       </c>
       <c r="P217" s="1"/>
       <c r="Q217" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R217" s="1" t="s">
         <v>30</v>
@@ -17916,7 +17916,7 @@
         <v>1135</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H218" s="1"/>
       <c r="I218" s="1"/>
@@ -17940,7 +17940,7 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R218" s="1" t="s">
         <v>30</v>
@@ -18090,7 +18090,7 @@
         <v>1279</v>
       </c>
       <c r="K221" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L221" s="1" t="s">
         <v>203</v>
@@ -18153,7 +18153,7 @@
         <v>1292</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M222" s="1" t="s">
         <v>1293</v>
@@ -18166,7 +18166,7 @@
       </c>
       <c r="P222" s="1"/>
       <c r="Q222" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R222" s="1" t="s">
         <v>30</v>
@@ -18217,7 +18217,7 @@
         <v>1299</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M223" s="1" t="s">
         <v>1300</v>
@@ -18290,7 +18290,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>26</v>
@@ -18350,7 +18350,7 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>26</v>
@@ -18414,7 +18414,7 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R226" s="1" t="s">
         <v>30</v>
@@ -18474,7 +18474,7 @@
       </c>
       <c r="P227" s="1"/>
       <c r="Q227" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R227" s="1" t="s">
         <v>30</v>
@@ -18538,7 +18538,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>30</v>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R229" s="1" t="s">
         <v>30</v>
@@ -18709,7 +18709,7 @@
         <v>165</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M231" s="1" t="s">
         <v>1358</v>
@@ -18722,7 +18722,7 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R231" s="1" t="s">
         <v>30</v>
@@ -18760,13 +18760,13 @@
         <v>27</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H232" s="1" t="s">
         <v>1364</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>1365</v>
@@ -18788,7 +18788,7 @@
       </c>
       <c r="P232" s="1"/>
       <c r="Q232" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R232" s="1" t="s">
         <v>30</v>
@@ -18848,7 +18848,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>30</v>
@@ -18901,7 +18901,7 @@
         <v>718</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M234" s="1" t="s">
         <v>1381</v>
@@ -18914,7 +18914,7 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R234" s="1" t="s">
         <v>30</v>
@@ -19028,7 +19028,7 @@
         <v>1398</v>
       </c>
       <c r="K236" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L236" s="1" t="s">
         <v>1399</v>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="P236" s="1"/>
       <c r="Q236" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R236" s="1" t="s">
         <v>30</v>
@@ -19110,7 +19110,7 @@
       </c>
       <c r="P237" s="1"/>
       <c r="Q237" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R237" s="1" t="s">
         <v>30</v>
@@ -19174,7 +19174,7 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R238" s="1" t="s">
         <v>30</v>
@@ -19232,7 +19232,7 @@
       </c>
       <c r="P239" s="1"/>
       <c r="Q239" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R239" s="1" t="s">
         <v>30</v>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="P241" s="1"/>
       <c r="Q241" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R241" s="1" t="s">
         <v>30</v>
@@ -19405,7 +19405,7 @@
         <v>1442</v>
       </c>
       <c r="L242" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M242" s="1" t="s">
         <v>1438</v>
@@ -19526,10 +19526,10 @@
         <v>1453</v>
       </c>
       <c r="K244" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L244" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M244" s="1" t="s">
         <v>1452</v>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="P244" s="1"/>
       <c r="Q244" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R244" s="1" t="s">
         <v>30</v>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="P245" s="1"/>
       <c r="Q245" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R245" s="1" t="s">
         <v>26</v>
@@ -19698,13 +19698,13 @@
         <v>27</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H247" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J247" s="1" t="s">
         <v>1464</v>
@@ -19788,7 +19788,7 @@
         <v>1478</v>
       </c>
       <c r="Q248" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R248" s="1" t="s">
         <v>30</v>
@@ -19901,7 +19901,7 @@
         <v>293</v>
       </c>
       <c r="L250" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M250" s="1" t="s">
         <v>1491</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="P250" s="1"/>
       <c r="Q250" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R250" s="1" t="s">
         <v>30</v>
@@ -19963,7 +19963,7 @@
         <v>293</v>
       </c>
       <c r="L251" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M251" s="1" t="s">
         <v>1491</v>
@@ -19976,7 +19976,7 @@
       </c>
       <c r="P251" s="1"/>
       <c r="Q251" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R251" s="1" t="s">
         <v>30</v>
@@ -20036,7 +20036,7 @@
       </c>
       <c r="P252" s="1"/>
       <c r="Q252" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R252" s="1" t="s">
         <v>30</v>
@@ -20505,7 +20505,7 @@
         <v>1557</v>
       </c>
       <c r="L260" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M260" s="1" t="s">
         <v>1558</v>
@@ -20518,7 +20518,7 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R260" s="1" t="s">
         <v>30</v>
@@ -20569,7 +20569,7 @@
         <v>1557</v>
       </c>
       <c r="L261" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M261" s="1" t="s">
         <v>1563</v>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="P261" s="1"/>
       <c r="Q261" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R261" s="1" t="s">
         <v>30</v>
@@ -20693,7 +20693,7 @@
         <v>561</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M263" s="1" t="s">
         <v>1579</v>
@@ -20706,7 +20706,7 @@
       </c>
       <c r="P263" s="1"/>
       <c r="Q263" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R263" s="1" t="s">
         <v>30</v>
@@ -20742,13 +20742,13 @@
         <v>27</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H264" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I264" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J264" s="1" t="s">
         <v>1585</v>
@@ -20770,7 +20770,7 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R264" s="1" t="s">
         <v>30</v>
@@ -20817,7 +20817,7 @@
         <v>293</v>
       </c>
       <c r="L265" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M265" s="1" t="s">
         <v>1593</v>
@@ -20890,7 +20890,7 @@
       </c>
       <c r="P266" s="1"/>
       <c r="Q266" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R266" s="1" t="s">
         <v>30</v>
@@ -20941,7 +20941,7 @@
         <v>1609</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>1610</v>
@@ -20954,7 +20954,7 @@
       </c>
       <c r="P267" s="1"/>
       <c r="Q267" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R267" s="1" t="s">
         <v>30</v>
@@ -21005,7 +21005,7 @@
         <v>718</v>
       </c>
       <c r="L268" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M268" s="1" t="s">
         <v>1615</v>
@@ -21067,7 +21067,7 @@
         <v>718</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1615</v>
@@ -21129,7 +21129,7 @@
         <v>59</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M270" s="1" t="s">
         <v>1627</v>
@@ -21193,7 +21193,7 @@
         <v>59</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M271" s="1" t="s">
         <v>1634</v>
@@ -21244,13 +21244,13 @@
         <v>209</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H272" s="1" t="s">
         <v>1643</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J272" s="1" t="s">
         <v>1644</v>
@@ -21274,7 +21274,7 @@
         <v>1647</v>
       </c>
       <c r="Q272" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R272" s="1" t="s">
         <v>30</v>
@@ -21310,13 +21310,13 @@
         <v>209</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H273" s="1" t="s">
         <v>1643</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>1644</v>
@@ -21340,7 +21340,7 @@
         <v>1647</v>
       </c>
       <c r="Q273" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R273" s="1" t="s">
         <v>30</v>
@@ -21404,7 +21404,7 @@
       </c>
       <c r="P274" s="1"/>
       <c r="Q274" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>30</v>
@@ -21466,7 +21466,7 @@
       </c>
       <c r="P275" s="1"/>
       <c r="Q275" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>30</v>
@@ -21530,7 +21530,7 @@
       </c>
       <c r="P276" s="1"/>
       <c r="Q276" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R276" s="1" t="s">
         <v>30</v>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="P277" s="1"/>
       <c r="Q277" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R277" s="1" t="s">
         <v>30</v>
@@ -21710,7 +21710,7 @@
       </c>
       <c r="P279" s="1"/>
       <c r="Q279" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R279" s="1" t="s">
         <v>30</v>
@@ -21772,7 +21772,7 @@
       </c>
       <c r="P280" s="1"/>
       <c r="Q280" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R280" s="1" t="s">
         <v>30</v>
@@ -22006,7 +22006,7 @@
       </c>
       <c r="P284" s="1"/>
       <c r="Q284" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R284" s="1" t="s">
         <v>30</v>
@@ -22074,7 +22074,7 @@
         <v>1738</v>
       </c>
       <c r="Q285" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R285" s="1" t="s">
         <v>30</v>
@@ -22109,7 +22109,7 @@
         <v>30</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G286" s="1" t="s">
         <v>1743</v>
@@ -22123,20 +22123,20 @@
         <v>1745</v>
       </c>
       <c r="L286" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M286" s="1" t="s">
         <v>1742</v>
       </c>
       <c r="N286" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O286" s="1" t="s">
         <v>1746</v>
       </c>
       <c r="P286" s="1"/>
       <c r="Q286" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R286" s="1" t="s">
         <v>30</v>
@@ -22169,7 +22169,7 @@
         <v>30</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G287" s="1"/>
       <c r="H287" s="1"/>
@@ -22181,20 +22181,20 @@
         <v>1750</v>
       </c>
       <c r="L287" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M287" s="1" t="s">
         <v>1742</v>
       </c>
       <c r="N287" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O287" s="1" t="s">
         <v>1751</v>
       </c>
       <c r="P287" s="1"/>
       <c r="Q287" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R287" s="1" t="s">
         <v>30</v>
